--- a/output/visualizacion_paralela_mamografia_dic_2025.xlsx
+++ b/output/visualizacion_paralela_mamografia_dic_2025.xlsx
@@ -2408,7 +2408,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Centro Comunitario de Salud Familiar Dr. José Symón Ojeda</t>
+          <t>CECOSF Haydeé Sepúlveda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hospital de Til Til</t>
+          <t>Hospital Comunitario de Til Til</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Centro Comunitario de Salud Familiar Lo Chacón</t>
+          <t>CECOSF Wilma Yoli Gomez Conejera</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Centro de Salud Familiar Maipo</t>
+          <t>Centro de Salud Familiar Dragica Ciudad Pap</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -16700,7 +16700,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Hospital de Til Til</t>
+          <t>Hospital Comunitario de Til Til</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
